--- a/data/trans_bre/KIDM_C_3_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/KIDM_C_3_R-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -665,12 +665,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 13,89</t>
+          <t>-14,05; 11,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 14,69</t>
+          <t>-11,68; 14,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 711,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 7,29</t>
+          <t>-6,62; 7,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 15,32</t>
+          <t>-6,35; 16,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 3,83</t>
+          <t>-7,24; 3,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 9,19</t>
+          <t>-5,26; 10,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-83,69; 327,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,2; 293,64</t>
+          <t>-45,68; 348,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,67</t>
+          <t>0,0; 11,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 17,89</t>
+          <t>-5,08; 19,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 0,0</t>
+          <t>-12,22; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 23,32</t>
+          <t>-3,95; 23,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,84</t>
+          <t>0,0; 10,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 13,11</t>
+          <t>-4,22; 12,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 11,13</t>
+          <t>-16,26; 11,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,09; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-85,41; 243,59</t>
+          <t>-84,28; 265,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,35; 6,52</t>
+          <t>-22,57; 7,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-27,33; 9,69</t>
+          <t>-28,09; 11,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,1</t>
+          <t>0,0; 22,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-87,52; 85,62</t>
+          <t>-100,0; 112,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,96</t>
+          <t>0,0; 15,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 9,51</t>
+          <t>-16,91; 10,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,06; 18,59</t>
+          <t>2,08; 16,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 12,9</t>
+          <t>-7,09; 13,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,32 +1260,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 3,43</t>
+          <t>-11,13; 3,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,08; 18,6</t>
+          <t>1,75; 19,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 8,92</t>
+          <t>-7,0; 9,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 7,5</t>
+          <t>-7,41; 6,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 142,28</t>
+          <t>-99,03; 162,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-22,18; —</t>
+          <t>-29,7; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 11,17</t>
+          <t>-4,39; 11,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 16,29</t>
+          <t>-6,92; 16,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 8,22</t>
+          <t>-11,27; 9,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 2,29</t>
+          <t>-3,42; 2,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,77; 250,26</t>
+          <t>-43,17; 266,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 74,77</t>
+          <t>-21,51; 75,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-44,61; 59,15</t>
+          <t>-44,94; 61,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 4,05</t>
+          <t>-1,46; 4,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 7,88</t>
+          <t>-0,94; 8,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 2,94</t>
+          <t>-4,86; 2,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 5,1</t>
+          <t>-0,88; 4,91</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-25,9; 139,95</t>
+          <t>-28,08; 142,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 77,65</t>
+          <t>-7,3; 85,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-38,98; 36,91</t>
+          <t>-42,29; 34,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-36,27; 561,79</t>
+          <t>-38,01; 569,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/KIDM_C_3_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/KIDM_C_3_R-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -665,12 +665,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 11,31</t>
+          <t>-12,39; 11,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 14,72</t>
+          <t>-10,41; 15,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 572,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 711,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 7,96</t>
+          <t>-6,16; 7,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 16,31</t>
+          <t>-6,01; 16,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 3,79</t>
+          <t>-7,44; 3,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 10,35</t>
+          <t>-4,81; 8,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-83,69; 327,44</t>
+          <t>-80,07; 451,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,68; 348,34</t>
+          <t>-46,42; 323,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,65</t>
+          <t>0,0; 12,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 19,09</t>
+          <t>-4,91; 18,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 0,0</t>
+          <t>-14,51; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 23,6</t>
+          <t>-1,86; 24,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -960,17 +960,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,48</t>
+          <t>0,0; 10,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 12,73</t>
+          <t>-4,0; 13,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 11,05</t>
+          <t>-16,0; 10,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-84,28; 265,8</t>
+          <t>-86,88; 211,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-22,57; 7,1</t>
+          <t>-23,31; 5,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 11,81</t>
+          <t>-28,07; 12,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,12</t>
+          <t>0,0; 17,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 112,72</t>
+          <t>-88,11; 106,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,36</t>
+          <t>0,0; 13,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 10,48</t>
+          <t>-16,8; 9,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,08; 16,73</t>
+          <t>2,08; 18,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 13,92</t>
+          <t>-6,83; 15,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,37 +1260,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 3,08</t>
+          <t>-11,62; 3,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 19,49</t>
+          <t>1,79; 19,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 9,13</t>
+          <t>-7,15; 8,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 6,7</t>
+          <t>-6,16; 7,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-99,03; 162,21</t>
+          <t>-100,0; 161,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-29,7; —</t>
+          <t>-17,24; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-80,05; 619,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 11,79</t>
+          <t>-3,37; 11,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 16,4</t>
+          <t>-7,48; 16,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 9,03</t>
+          <t>-12,21; 8,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 2,31</t>
+          <t>-3,49; 2,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-43,17; 266,03</t>
+          <t>-34,56; 244,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,51; 75,03</t>
+          <t>-23,04; 77,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-44,94; 61,04</t>
+          <t>-46,85; 60,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 4,06</t>
+          <t>-1,51; 4,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 8,2</t>
+          <t>-0,73; 7,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 2,84</t>
+          <t>-4,68; 2,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 4,91</t>
+          <t>-0,71; 5,08</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-28,08; 142,54</t>
+          <t>-30,37; 149,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 85,02</t>
+          <t>-5,5; 83,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-42,29; 34,79</t>
+          <t>-39,86; 34,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 569,29</t>
+          <t>-31,76; 617,21</t>
         </is>
       </c>
     </row>
